--- a/administrasi/Daftar Hadir Ujian.xlsx
+++ b/administrasi/Daftar Hadir Ujian.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ZEN-PROJECT\semester-pkbm\administrasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1B3CAC-30F7-47A3-B1B0-0CBBCDCDCBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B79C00-8D7D-43AE-ACDA-AC03800935A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bangun Rejo" sheetId="1" r:id="rId1"/>
@@ -587,6 +587,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -613,9 +616,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1112,119 +1112,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
     </row>
     <row r="2" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="40" t="s">
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="40" t="s">
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="40" t="s">
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="41"/>
+      <c r="N6" s="42"/>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="40" t="s">
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="40" t="s">
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="40" t="s">
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="40" t="s">
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="N7" s="41"/>
+      <c r="N7" s="42"/>
     </row>
     <row r="8" spans="1:14" ht="38.1" customHeight="1">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="A8" s="42"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="18" t="s">
         <v>11</v>
       </c>
@@ -1376,7 +1376,7 @@
       <c r="B14" s="25">
         <v>3116653493</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="36" t="s">
         <v>70</v>
       </c>
       <c r="D14" s="12"/>
@@ -1544,6 +1544,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -1551,13 +1558,6 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1580,118 +1580,118 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
     </row>
     <row r="4" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="24" customHeight="1">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="40" t="s">
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="40" t="s">
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="40" t="s">
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="41"/>
+      <c r="N5" s="42"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="24" customHeight="1">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="40" t="s">
+      <c r="A6" s="42"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="40" t="s">
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="40" t="s">
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="40" t="s">
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="41"/>
+      <c r="N6" s="42"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="36" customHeight="1">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="18" t="s">
         <v>11</v>
       </c>
@@ -2036,6 +2036,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -2043,13 +2050,6 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2068,13 +2068,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -2087,13 +2087,13 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -2106,13 +2106,13 @@
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -2144,7 +2144,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="37" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="34" t="s">
@@ -2159,7 +2159,7 @@
       <c r="E7" s="34"/>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A8" s="36"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="10" t="s">
         <v>12</v>
       </c>
@@ -2172,7 +2172,7 @@
       <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A9" s="36"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="34" t="s">
         <v>13</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="E9" s="34"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -2195,12 +2195,12 @@
         <v>67</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A11" s="36"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="34" t="s">
         <v>15</v>
       </c>
@@ -2213,7 +2213,7 @@
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="11" t="s">
         <v>16</v>
       </c>
@@ -2226,7 +2226,7 @@
       <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="37" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="34" t="s">
@@ -2236,12 +2236,12 @@
         <v>67</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E13" s="34"/>
     </row>
     <row r="14" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A14" s="36"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="10" t="s">
         <v>18</v>
       </c>
@@ -2254,7 +2254,7 @@
       <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A15" s="36"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="34" t="s">
         <v>19</v>
       </c>
@@ -2267,7 +2267,7 @@
       <c r="E15" s="34"/>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="37" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -2282,7 +2282,7 @@
       <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A17" s="36"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="35" t="s">
         <v>21</v>
       </c>
@@ -2342,13 +2342,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -2361,13 +2361,13 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -2380,13 +2380,13 @@
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -2418,7 +2418,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="37" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="34" t="s">
@@ -2434,7 +2434,7 @@
       <c r="E7" s="34"/>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A8" s="36"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="10" t="s">
         <v>12</v>
       </c>
@@ -2448,7 +2448,7 @@
       <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A9" s="36"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="34" t="s">
         <v>13</v>
       </c>
@@ -2462,7 +2462,7 @@
       <c r="E9" s="34"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="D10" s="11" t="str">
         <f>'Pengawas Bangun Rejo'!D10</f>
-        <v>Zakki Azhar</v>
+        <v>Muhammad Zaini, S.Psi.</v>
       </c>
       <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A11" s="36"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="34" t="s">
         <v>15</v>
       </c>
@@ -2492,7 +2492,7 @@
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="11" t="s">
         <v>16</v>
       </c>
@@ -2506,7 +2506,7 @@
       <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="37" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="34" t="s">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="D13" s="34" t="str">
         <f>'Pengawas Bangun Rejo'!D13</f>
-        <v>Muhammad Zaini, S.Psi.</v>
+        <v>Zakki Azhar</v>
       </c>
       <c r="E13" s="34"/>
     </row>
     <row r="14" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A14" s="36"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="10" t="s">
         <v>18</v>
       </c>
@@ -2536,7 +2536,7 @@
       <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A15" s="36"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="34" t="s">
         <v>19</v>
       </c>
@@ -2550,7 +2550,7 @@
       <c r="E15" s="34"/>
     </row>
     <row r="16" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="37" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -2566,7 +2566,7 @@
       <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="30.95" customHeight="1">
-      <c r="A17" s="36"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="35" t="s">
         <v>21</v>
       </c>

--- a/administrasi/Daftar Hadir Ujian.xlsx
+++ b/administrasi/Daftar Hadir Ujian.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ZEN-PROJECT\semester-pkbm\administrasi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\semester-pkbm\administrasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B79C00-8D7D-43AE-ACDA-AC03800935A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B572291-A990-4DBF-94F4-B4207BA625E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bangun Rejo" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,10 @@
     <sheet name="Pengawas Bangun Rejo" sheetId="5" r:id="rId3"/>
     <sheet name="Pengawas Bunda" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Pengawas Bangun Rejo'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Pengawas Bunda'!$A$1:$E$17</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1544,6 +1548,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:N6"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
@@ -1551,13 +1562,6 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:N6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2036,6 +2040,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:N5"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="J6:L6"/>
@@ -2043,13 +2054,6 @@
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="C5:C7"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:N5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2057,6 +2061,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D51CD7-B317-4F4C-A0A5-D60D0DA035EA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:XES22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2166,10 +2173,10 @@
       <c r="C8" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
       <c r="A9" s="37"/>
@@ -2221,7 +2228,7 @@
         <v>69</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E12" s="11"/>
     </row>
@@ -2236,7 +2243,7 @@
         <v>67</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E13" s="34"/>
     </row>
@@ -2248,10 +2255,10 @@
       <c r="C14" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="11"/>
+      <c r="D14" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:15" s="2" customFormat="1" ht="30.95" customHeight="1">
       <c r="A15" s="37"/>
@@ -2277,7 +2284,7 @@
         <v>67</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E16" s="11"/>
     </row>
@@ -2290,7 +2297,7 @@
         <v>68</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E17" s="34"/>
     </row>
@@ -2326,11 +2333,15 @@
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup scale="85" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:XES22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2501,7 +2512,7 @@
       </c>
       <c r="D12" s="11" t="str">
         <f>'Pengawas Bangun Rejo'!D12</f>
-        <v>Wahidi Rahman Al-Anshori</v>
+        <v>Ibnaty Raniah Muyassarah</v>
       </c>
       <c r="E12" s="11"/>
     </row>
@@ -2517,7 +2528,7 @@
       </c>
       <c r="D13" s="34" t="str">
         <f>'Pengawas Bangun Rejo'!D13</f>
-        <v>Zakki Azhar</v>
+        <v>Chairid Daha, A.Md.</v>
       </c>
       <c r="E13" s="34"/>
     </row>
@@ -2531,7 +2542,7 @@
       </c>
       <c r="D14" s="10" t="str">
         <f>'Pengawas Bangun Rejo'!D14</f>
-        <v>Akhmad Yudha Nugraha, S.Pd.</v>
+        <v>Zakki Azhar</v>
       </c>
       <c r="E14" s="11"/>
     </row>
@@ -2561,7 +2572,7 @@
       </c>
       <c r="D16" s="11" t="str">
         <f>'Pengawas Bangun Rejo'!D16</f>
-        <v>Ibnaty Raniah Muyassarah</v>
+        <v>Wahidi Rahman Al-Anshori</v>
       </c>
       <c r="E16" s="11"/>
     </row>
@@ -2575,7 +2586,7 @@
       </c>
       <c r="D17" s="34" t="str">
         <f>'Pengawas Bangun Rejo'!D17</f>
-        <v>Chairid Daha, A.Md.</v>
+        <v>Akhmad Yudha Nugraha, S.Pd.</v>
       </c>
       <c r="E17" s="34"/>
     </row>
@@ -2611,5 +2622,6 @@
     <mergeCell ref="A10:A12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup scale="85" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/administrasi/Daftar Hadir Ujian.xlsx
+++ b/administrasi/Daftar Hadir Ujian.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\semester-pkbm\administrasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B572291-A990-4DBF-94F4-B4207BA625E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8841C7-7E7A-4A47-8215-72787925FA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bangun Rejo" sheetId="1" r:id="rId1"/>
     <sheet name="Bunda" sheetId="2" r:id="rId2"/>
     <sheet name="Pengawas Bangun Rejo" sheetId="5" r:id="rId3"/>
     <sheet name="Pengawas Bunda" sheetId="4" r:id="rId4"/>
+    <sheet name="Jumlah Anak" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Pengawas Bangun Rejo'!$A$1:$E$17</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="71">
   <si>
     <t>DAFTAR HADIR PESERTA UJIAN PENDIDIKAN KESETARAAN</t>
   </si>
@@ -1548,6 +1549,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -1555,13 +1563,6 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2040,6 +2041,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -2047,13 +2055,6 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2624,4 +2625,91 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="85" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7778BAE0-192A-45BA-904F-F1D4FACC4787}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75">
+      <c r="A2" s="34"/>
+      <c r="D2">
+        <f>9*20</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="A3" s="10"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75">
+      <c r="A4" s="34"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75">
+      <c r="A5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="31.5">
+      <c r="A6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75">
+      <c r="A7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75">
+      <c r="A8" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75">
+      <c r="A9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75">
+      <c r="A10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75">
+      <c r="A13" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>